--- a/Result/profitability/2707.xlsx
+++ b/Result/profitability/2707.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>3.68</v>
       </c>
       <c r="M2" t="n">
-        <v>3.2175</v>
+        <v>3.36125</v>
       </c>
       <c r="N2" t="n">
-        <v>34.1425</v>
+        <v>34.82125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>2.21</v>
       </c>
       <c r="M3" t="n">
-        <v>3.27625</v>
+        <v>3.24125</v>
       </c>
       <c r="N3" t="n">
-        <v>36.2375</v>
+        <v>36.42125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>2.3</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1675</v>
+        <v>3.13375</v>
       </c>
       <c r="N4" t="n">
-        <v>37.91875</v>
+        <v>37.8625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>2.41</v>
       </c>
       <c r="M5" t="n">
-        <v>3.07375</v>
+        <v>3.13</v>
       </c>
       <c r="N5" t="n">
-        <v>38.745</v>
+        <v>38.93625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>2.88</v>
       </c>
       <c r="M6" t="n">
-        <v>3.12875</v>
+        <v>3.19875</v>
       </c>
       <c r="N6" t="n">
-        <v>39.78125</v>
+        <v>40.26499999999999</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>2.3</v>
       </c>
       <c r="M7" t="n">
-        <v>3.125</v>
+        <v>3.05</v>
       </c>
       <c r="N7" t="n">
-        <v>41.70625</v>
+        <v>41.55625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>2.06</v>
       </c>
       <c r="M8" t="n">
-        <v>2.94625</v>
+        <v>2.59125</v>
       </c>
       <c r="N8" t="n">
-        <v>43.57875</v>
+        <v>43.2675</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1775,7 +1775,7 @@
         <v>2.565</v>
       </c>
       <c r="N11" t="n">
-        <v>41.89</v>
+        <v>41.88999999999999</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2707</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1664</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1107</v>
+      </c>
+      <c r="E75" t="n">
+        <v>557</v>
+      </c>
+      <c r="F75" t="n">
+        <v>33.46</v>
+      </c>
+      <c r="G75" t="n">
+        <v>422</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>25.38%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>47</v>
+      </c>
+      <c r="J75" t="n">
+        <v>470</v>
+      </c>
+      <c r="K75" t="n">
+        <v>369</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="M75" t="n">
+        <v>3.11875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>32.44</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-2.84</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.4956369982547993</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.490000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.06926286509040336</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.4500000000000002</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.1844262295081969</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.530000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.04791731913560926</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
